--- a/Outputs/Scenarios/PtX_demand_IE_Hydrogen.xlsx
+++ b/Outputs/Scenarios/PtX_demand_IE_Hydrogen.xlsx
@@ -1037,7 +1037,7 @@
         <v>1.495982210596268e-05</v>
       </c>
       <c r="K16" t="n">
-        <v>0.003882960145141249</v>
+        <v>0.002111915457780947</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.001294320048380416</v>
+        <v>0.003051779348884794</v>
       </c>
     </row>
     <row r="18">
@@ -1481,7 +1481,7 @@
         <v>2.15545713815099e-07</v>
       </c>
       <c r="K28" t="n">
-        <v>0.001294320048380416</v>
+        <v>0.001307905435236341</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>2.214619532340416e-05</v>
       </c>
       <c r="K30" t="n">
-        <v>0.02095286641555635</v>
+        <v>0.01139612069498154</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.00698428880518545</v>
+        <v>0.01646772633166199</v>
       </c>
     </row>
     <row r="32">
@@ -1999,7 +1999,7 @@
         <v>1.165589227547588e-06</v>
       </c>
       <c r="K42" t="n">
-        <v>0.00698428880518545</v>
+        <v>0.007057596999283712</v>
       </c>
     </row>
     <row r="43">
